--- a/tools/excel/ncsc/ncsc-caf-4.0-igp.xlsx
+++ b/tools/excel/ncsc/ncsc-caf-4.0-igp.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>National Cyber Security Centre - Cyber Assessment Framework, assessed the way the framework is designed to be used: the contributing outcome is the unit of assessment, and every indicator of good practice is answered true or false. Each outcome closes with a status question that turns those answers into Achieved, Partially achieved or Not achieved.
+          <t>National Cyber Security Centre - Cyber Assessment Framework, assessed the way the framework is designed to be used: the contributing outcome is the unit of assessment, and every indicator of good practice is answered true or false. Those answers decide the outcome status - Achieved, Partially achieved or Not achieved - by the rule the indicator tables print.
 https://www.ncsc.gov.uk/collection/cyber-assessment-framework</t>
         </is>
       </c>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>National Cyber Security Centre - Cyber Assessment Framework, assessed the way the framework is designed to be used: the contributing outcome is the unit of assessment, and every indicator of good practice is answered true or false. Each outcome closes with a status question that turns those answers into Achieved, Partially achieved or Not achieved.
+          <t>National Cyber Security Centre - Cyber Assessment Framework, assessed the way the framework is designed to be used: the contributing outcome is the unit of assessment, and every indicator of good practice is answered true or false. Those answers decide the outcome status - Achieved, Partially achieved or Not achieved - by the rule the indicator tables print.
 https://www.ncsc.gov.uk/collection/cyber-assessment-framework</t>
         </is>
       </c>
@@ -676,6 +676,18 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>tiered_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>field_visibility</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>{"score": {"auditor": "hidden", "respondent": "hidden"}, "documentation_score": {"auditor": "hidden", "respondent": "hidden"}, "extended_result": {"auditor": "hidden", "respondent": "hidden"}, "status": {"auditor": "hidden", "respondent": "hidden"}}</t>
         </is>
       </c>
     </row>
@@ -1407,16 +1419,17 @@
           <t>[A4.b.NA.1] Your software supplier(s) is unaware of the composition and provenance of software provided to you.
 [A4.b.NA.2] Software, including updates and patches, undergoes little to no testing.
 [A4.b.NA.3] Updates and patches often introduce new problems or fail to address existing issues.
-[A4.b.NA.4] Vulnerabilities are discovered in software despite the negligible difficulty of implementing mitigations. be appropriate and proportionate within the context of common threats.
+[A4.b.NA.4] Vulnerabilities are discovered in software despite the negligible difficulty of implementing mitigations.
 [A4.b.PA.1] Your software supplier leverages secure development principles and practices.
 [A4.b.PA.2] Your software supplier(s) can demonstrate a limited understanding of the composition and provenance of software provided to you.
-[A4.b.PA.3] You consider the security of environments (e.g. development, test and production), including source code and repositories, used in the production of software to The testing regime uses a range of different approaches (e.g. static and dynamic analysis, unit and integration testing and point in time assessments) that verify all aspects of the development lifecycle covering both functional and non-functional testing.
-[A4.b.PA.4] You have arrangements in place with your software supplier to receive timely security updates, patches and notifications.
-[A4.b.PA.5] Software, including updates and patches, is obtained from your supplier(s) via secure channels.
-[A4.b.PA.6] Your software supplier(s) has processes in place to identify, report and mitigate security vulnerabilities.
-[A4.b.PA.7] You have arrangements in place with your software supplier to be notified of any significant events that may adversely impact network and information systems supporting your essential function(s).
-[A4.b.PA.8] If open-source software is used, you have taken appropriate and proportionate steps to establish and maintain sufficient confidence in its security for its use.
-[A4.b.PA.9] You have appropriate support and maintenance arrangements in place.
+[A4.b.PA.3] You consider the security of environments (e.g. development, test and production), including source code and repositories, used in the production of software to be appropriate and proportionate within the context of common threats.
+[A4.b.PA.4] The testing regime uses a range of different approaches (e.g. static and dynamic analysis, unit and integration testing and point in time assessments) that verify all aspects of the development lifecycle covering both functional and non-functional testing.
+[A4.b.PA.5] You have arrangements in place with your software supplier to receive timely security updates, patches and notifications.
+[A4.b.PA.6] Software, including updates and patches, is obtained from your supplier(s) via secure channels.
+[A4.b.PA.7] Your software supplier(s) has processes in place to identify, report and mitigate security vulnerabilities.
+[A4.b.PA.8] You have arrangements in place with your software supplier to be notified of any significant events that may adversely impact network and information systems supporting your essential function(s).
+[A4.b.PA.9] If open-source software is used, you have taken appropriate and proportionate steps to establish and maintain sufficient confidence in its security for its use.
+[A4.b.PA.10] You have appropriate support and maintenance arrangements in place.
 [A4.b.A.1] Your software supplier(s) leverages an established secure software development framework (e.g. NIST Secure Software Development Framework (SSDF), Microsoft Secure Development Lifecycle (SDL)).
 [A4.b.A.2] Your software supplier can demonstrate a thorough understanding of the composition and provenance of software provided to you, including any third-party components used in the development of that software, and those components are being monitored for new vulnerabilities throughout the lifespan of the product.
 [A4.b.A.3] You consider the security of environments (e.g. development, test, and production), including source code and repositories, used in the production of software to be appropriate and proportionate within the context of capable and well-resourced threat actors.
@@ -1430,6 +1443,7 @@
 TF-NA
 TF-NA
 TF-NA
+TF-PA
 TF-PA
 TF-PA
 TF-PA

--- a/tools/excel/ncsc/ncsc-caf-4.0-igp.xlsx
+++ b/tools/excel/ncsc/ncsc-caf-4.0-igp.xlsx
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -710,9 +710,10 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="120" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="120" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,17 +744,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>annotation</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>answer</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>question_group_color</t>
         </is>
       </c>
     </row>
@@ -780,6 +786,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -804,6 +811,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -830,11 +838,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>[A1.a.NA.1] The security of network and information systems related to the operation of essential function(s) is not discussed or reported on regularly at board-level.
 [A1.a.NA.2] Board-level discussions on the security of network and information systems are based on partial or out-of-date information, without the benefit of expert guidance.
@@ -848,18 +851,46 @@
 [A1.a.A.6] Security is recognised as an important enabler for the resilience of your essential function(s) and considered in all relevant discussions.</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -888,11 +919,6 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>[A1.b.NA.1] Key roles are missing, left vacant, or fulfilled on an ad-hoc or informal basis.
 [A1.b.NA.2] Staff are assigned security responsibilities but without adequate authority or resources to fulfil them.
@@ -902,14 +928,34 @@
 [A1.b.A.3] There is clarity on who in your organisation has overall accountability for the security of network and information systems supporting your essential function(s).</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -938,11 +984,6 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>[A1.c.NA.1] What should be relatively straightforward risk decisions are constantly referred up the chain, or not made.
 [A1.c.NA.2] Risks are resolved informally (or ignored) at a local level when the use of a more formal risk reporting mechanism would be more appropriate.
@@ -956,18 +997,46 @@
 [A1.c.A.4] Risk management decisions are regularly reviewed to ensure their continued relevance and validity.</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -994,6 +1063,7 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1020,11 +1090,6 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>[A2.a.NA.1] Risk assessments are not based on a clearly defined set of threat assumptions.
 [A2.a.NA.2] Risk assessment outputs are too complex or unwieldy to be consumed by decision-makers and are not effectively communicated in a clear and timely manner.
@@ -1050,30 +1115,82 @@
 [A2.a.A.9] You anticipate technological developments that could be used to adversely impact network and information systems supporting your essential function(s).</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1102,11 +1219,6 @@
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>[A2.b.NA.1] You are unable to perform threat analysis.
 [A2.b.NA.2] You do not understand the threats to network and information systems supporting your essential function(s).
@@ -1127,25 +1239,67 @@
 [A2.b.A.8] You have documented the steps required to undertake detailed threat analysis.</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1174,11 +1328,6 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>[A2.c.NA.1] A particular product or service is seen as a "silver bullet" and vendor claims are taken at face value.
 [A2.c.NA.2] Assurance methods are applied without appreciation of their strengths and limitations.
@@ -1190,16 +1339,40 @@
 [A2.c.A.5] The methods used for assurance are reviewed to ensure they are working as intended and remain the most appropriate method to use.</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1226,6 +1399,7 @@
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1248,11 +1422,6 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>[A3.a.NA.1] Inventories of assets relevant to network and information systems supporting your essential function(s) are incomplete, non-existent or inadequately detailed.
 [A3.a.NA.2] Only certain domains or types of asset are documented and understood. Dependencies between assets are not understood (such as the dependencies between IT and OT).
@@ -1266,18 +1435,46 @@
 [A3.a.A.5] Assets relevant to network and information systems supporting your essential function(s) are managed with cyber security in mind throughout their lifecycle, from creation through to eventual decommissioning or disposal.</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1304,6 +1501,7 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1330,11 +1528,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>[A4.a.NA.1] You do not know what data belonging to you is held by suppliers, or how it is managed.
 [A4.a.NA.2] Elements of the supply chain for network and information systems supporting your essential function(s) are subcontracted and you have little or no visibility of the sub-contractors.
@@ -1359,29 +1552,79 @@
 [A4.a.A.10] When appropriate, your incident management process and that of your suppliers provide mutual support in the resolution of incidents.</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1653,6 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>[A4.b.NA.1] Your software supplier(s) is unaware of the composition and provenance of software provided to you.
 [A4.b.NA.2] Software, including updates and patches, undergoes little to no testing.
@@ -1437,27 +1675,73 @@
 [A4.b.A.5] You can attest to the authenticity and integrity of software, including updates and patches.</t>
         </is>
       </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1484,6 +1768,7 @@
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1508,6 +1793,7 @@
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1534,11 +1820,6 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>[B1.a.NA.1] Your policies, processes and procedures are absent or incomplete.
 [B1.a.NA.2] Policies, processes and procedures are not applied universally or consistently.
@@ -1558,24 +1839,64 @@
 [B1.a.A.7] Your systems are designed so that they remain secure even when user security policies, processes and procedures are not always followed.</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1604,11 +1925,6 @@
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>[B1.b.NA.1] Policies, processes and procedures are ignored or only partially followed.
 [B1.b.NA.2] How your policies, processes and procedures support the resilience of your essential function(s) is not well understood.
@@ -1626,22 +1942,58 @@
 [B1.b.A.4] Appropriate action is taken to address all breaches of policies, processes and procedures with potential to adversely impact the essential function(s) including aggregated breaches.</t>
         </is>
       </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1668,6 +2020,7 @@
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1694,11 +2047,6 @@
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>[B2.a.NA.1] Initial identity verification is not robust enough to provide an acceptable level of confidence of a user's identity profile.
 [B2.a.NA.2] Authorised users and systems with access to networks or information systems on which your essential function(s) depends cannot be individually identified.
@@ -1720,26 +2068,70 @@
 [B2.a.A.6] Your approach to authenticating users, devices and systems follows up to date best practice.</t>
         </is>
       </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1768,11 +2160,6 @@
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>[B2.b.NA.1] Users can connect to network and information systems supporting your essential function(s) using devices that are not corporately owned and managed.
 [B2.b.NA.2] Privileged users can perform privileged operations from devices that are not corporately owned and managed.
@@ -1789,21 +2176,55 @@
 [B2.b.A.4] You perform regular scans to detect unknown devices and investigate any findings.</t>
         </is>
       </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1832,11 +2253,6 @@
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>[B2.c.NA.1] The identities of the individuals with privileged access to network and information systems (infrastructure, platforms, software, configuration etc) supporting your essential function(s) are not known or not managed.
 [B2.c.NA.2] Privileged user access to network and information systems supporting your essential function(s) is via weak authentication mechanisms (e.g. only simple passwords).
@@ -1855,23 +2271,61 @@
 [B2.c.A.4] All privileged user activity is routinely reviewed, validated and recorded for offline analysis and investigation.</t>
         </is>
       </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1900,11 +2354,6 @@
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>[B2.d.NA.1] Greater access rights are granted than necessary.
 [B2.d.NA.2] Identity validation and requirement for access of a user, device or systems is not carried out.
@@ -1922,22 +2371,58 @@
 [B2.d.A.5] Attempts by unauthorised users, devices or systems to connect to network and information systems supporting your essential function(s) are alerted, promptly assessed and investigated.</t>
         </is>
       </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -1964,6 +2449,7 @@
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1990,11 +2476,6 @@
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>[B3.a.NA.1] You have incomplete knowledge of what data is used by and produced in the operation of network and information systems supporting your essential function(s).
 [B3.a.NA.2] You have not identified the important data on which network and information systems supporting your essential function(s) relies.
@@ -2017,27 +2498,73 @@
 [B3.a.A.9] You validate these documented impact statements regularly, at least annually.</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2066,11 +2593,6 @@
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>[B3.b.NA.1] You do not know what all your data links are, or which carry data important to the operation of the essential function(s).
 [B3.b.NA.2] Data important to the operation of the essential function(s) travels without technical protection over non-trusted or openly accessible carriers.
@@ -2082,16 +2604,40 @@
 [B3.b.A.3] Suitable alternative transmission paths are available where there is a significant risk of impact on the operation of the essential function(s) due to resource limitation (e.g. transmission equipment or function failure, or important data being blocked or jammed).</t>
         </is>
       </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2120,11 +2666,6 @@
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>[B3.c.NA.1] You have no, or limited, knowledge of where data important to the operation of network and information systems supporting your essential function(s) is stored.
 [B3.c.NA.2] You have not protected vulnerable stored data important to the operation of network and information systems supporting your essential function(s) in a suitable way.
@@ -2140,20 +2681,52 @@
 [B3.c.A.5] Necessary historic or archive data is suitably secured in storage.</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2182,11 +2755,6 @@
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>[B3.d.NA.1] You do not know which mobile devices may hold data important to the operation of network and information systems supporting your essential function(s).
 [B3.d.NA.2] You allow data important to the operation of network and information systems supporting your essential function(s) to be stored on devices not managed by your organisation, or to at least equivalent standard.
@@ -2199,17 +2767,43 @@
 [B3.d.A.3] You have minimised this data on these mobile devices. Some data may be automatically deleted off mobile devices after a certain period.</t>
         </is>
       </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2238,11 +2832,6 @@
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>[B3.e.NA.1] Some or all devices, equipment or removable media that hold data important to the operation of network and information systems supporting your essential function(s) are reused or disposed of without sanitisation of that data.
 [B3.e.PA.1] Data important to the operations of network and information systems supporting your essential function(s) is removed from all devices, equipment and removable media before reuse and / or disposal.
@@ -2250,12 +2839,28 @@
 [B3.e.A.2] Data important to the operation of network and information systems supporting your essential function(s) is removed from all devices, equipment and removable media before reuse and / or disposal using an assured product or service.</t>
         </is>
       </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-PA
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-PA
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#D97706
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2282,6 +2887,7 @@
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2308,11 +2914,6 @@
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>[B4.a.NA.1] Network and information systems supporting the operation of the essential function(s) are not appropriately segregated from other systems.
 [B4.a.NA.2] Internet services, such as browsing and email are accessible from network and information systems supporting your essential function(s).
@@ -2331,23 +2932,61 @@
 [B4.a.A.6] If automated decision-making technologies are in use, you design and apply appropriate restrictions to prevent actions that could have an adverse impact on network and information systems supporting your essential function(s).</t>
         </is>
       </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2376,11 +3015,6 @@
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>[B4.b.NA.1] You have not identified the assets that need to be carefully configured to maintain the security of network and information systems supporting your essential function(s).
 [B4.b.NA.2] Policies relating to the security of operating system builds or configuration are not applied consistently across network and information systems relating to your essential function(s).
@@ -2404,28 +3038,76 @@
 [B4.b.A.7] Generic, shared, default name and built-in accounts have been removed or disabled. Where this is not possible, credentials to these accounts have been changed. Service accounts are appropriately protected.</t>
         </is>
       </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2454,11 +3136,6 @@
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>[B4.c.NA.1] Your systems and devices supporting the operation of the essential function(s) are administered or maintained from devices that are not corporately owned and managed.
 [B4.c.NA.2] You do not have good or current technical documentation of network and information systems.
@@ -2470,16 +3147,40 @@
 [B4.c.A.3] You prevent, detect and remove malware, and unauthorised software. You use technical, procedural and physical measures as necessary.</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2508,11 +3209,6 @@
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>[B4.d.NA.1] You do not understand the exposure of network and information systems supporting your essential function(s) to publicly-known vulnerabilities.
 [B4.d.NA.2] You do not mitigate externally exposed vulnerabilities promptly.
@@ -2530,22 +3226,58 @@
 [B4.d.A.4] You actively maximise the use of supported software, firmware and hardware in network and information systems supporting your essential function(s).</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2572,6 +3304,7 @@
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2598,11 +3331,6 @@
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>[B5.a.NA.1] You have limited understanding of all the elements that are required to restore operation of network and information systems supporting your essential function(s).
 [B5.a.NA.2] You have not completed business continuity and disaster recovery plans for network and information systems, including their dependencies, supporting the operation of the essential function(s).
@@ -2613,15 +3341,37 @@
 [B5.a.A.2] You use your security awareness and threat intelligence sources to identify new or heightened levels of risk, which result in immediate and potentially temporary security measures to enhance the security of network and information systems supporting your essential function(s), (e.g. in response to a widespread outbreak of very damaging malware).</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2650,11 +3400,6 @@
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>[B5.b.NA.1] Network and information systems supporting the operation of your essential function(s) are not appropriately segregated.
 [B5.b.NA.2] Internet services, such as browsing and email, are accessible from network and information systems supporting your essential function(s).
@@ -2669,19 +3414,49 @@
 [B5.b.A.5] You review and update assessments of dependencies, resource and geographical limitations and mitigations when necessary.</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2710,11 +3485,6 @@
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>[B5.c.NA.1] Backup coverage is incomplete and does not include all relevant data and information needed to restore the operation of your essential function(s).
 [B5.c.NA.2] Backups are not frequent enough for the operation of your essential function(s) to be restored effectively.
@@ -2725,15 +3495,37 @@
 [B5.c.A.2] Backups of all important data and information needed to recover the essential function(s) are made, tested, documented and routinely reviewed.</t>
         </is>
       </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2760,6 +3552,7 @@
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2786,11 +3579,6 @@
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>[B6.a.NA.1] People in your organisation do not understand what they contribute to the cyber security of network and information systems supporting your essential function(s).
 [B6.a.NA.2] People in your organisation do not know how to raise a concern about cyber security.
@@ -2809,23 +3597,61 @@
 [B6.a.A.6] People across your organisation collaborate in cyber security activities and improvements, building joint ownership and bringing knowledge of their area of expertise.</t>
         </is>
       </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2854,11 +3680,6 @@
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>[B6.b.NA.1] There are teams who operate and support your essential function(s) that lack any cyber security training.
 [B6.b.NA.2] Cyber security training is restricted to specific roles in your organisation.
@@ -2875,21 +3696,55 @@
 [B6.b.A.4] You make cyber security information and good practice guidance easily accessible, widely available and you know it is referenced and used within your organisation.</t>
         </is>
       </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -2916,6 +3771,7 @@
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2940,6 +3796,7 @@
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2966,11 +3823,6 @@
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>[C1.a.NA.1] Data relating to the security and operation of network and information systems supporting your essential function(s) is not collected.
 [C1.a.NA.2] You are not able to audit the activities of users and systems in relation to network and information systems supporting your essential function(s).
@@ -2999,33 +3851,91 @@
 [C1.a.A.9] You regularly review the data sources and tools included in your logging and monitoring strategy to ensure it remains effective.</t>
         </is>
       </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3054,11 +3964,6 @@
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>[C1.b.NA.1] It is possible for log data to be easily edited or deleted by unauthorised users / systems or attackers.
 [C1.b.NA.2] There is no control of the users and systems that can access log data.
@@ -3075,21 +3980,55 @@
 [C1.b.A.5] The integrity of log data is protected, verified and any modification, including deletion, is detected and attributed.</t>
         </is>
       </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3118,11 +4057,6 @@
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>[C1.c.NA.1] You do not apply updates to your detection security technologies in a timely way, after receiving them (e.g. AV signature updates, other threat signatures or Indicators of Compromise (IoCs)).
 [C1.c.NA.2] Security alerts relating to network and information systems supporting your essential function(s) are not prioritised.
@@ -3150,32 +4084,88 @@
 [C1.c.A.9] Logs are monitored continuously in near real time.</t>
         </is>
       </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3204,11 +4194,6 @@
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>[C1.d.NA.1] You do not triage alerts from your detection security technologies (e.g. AV, IDS).
 [C1.d.NA.2] You do not categorise alerts and incidents by type and priority / severity level.
@@ -3228,24 +4213,64 @@
 [C1.d.A.6] Your understanding of normal user and system behaviour, and threats, is sufficient for effective decision making within triage.</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3274,11 +4299,6 @@
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>[C1.e.NA.1] There are no personnel who perform a monitoring and detection function.
 [C1.e.NA.2] Monitoring and detection personnel do not have the correct specialist skills.
@@ -3303,29 +4323,79 @@
 [C1.e.A.9] Monitoring and detection personnel deal with their workload and cases effectively as well as identifying areas for improvement.</t>
         </is>
       </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3354,11 +4424,6 @@
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>[C1.f.NA.1] Your organisation has no sources of threat intelligence.
 [C1.f.NA.2] You do not evaluate the usefulness of your threat intelligence or share feedback with providers or other users.
@@ -3381,27 +4446,73 @@
 [C1.f.A.8] You possess the capability to share threat intelligence (e.g. ways to effectively detect adversaries) with the threat community / defender community (sector partners, threat intelligence providers, government agencies) when required.</t>
         </is>
       </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3428,6 +4539,7 @@
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3450,11 +4562,6 @@
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>[C2.a.NA.1] You do not know the resources required for threat hunting.
 [C2.a.NA.2] You do not have access to an effective threat hunting capability.
@@ -3473,23 +4580,61 @@
 [C2.a.A.8] Your threat hunts focus on the tactics, techniques and procedures (TTPs) of threats over atomic IoCs (e.g. hashes, IP addresses, domain names etc).</t>
         </is>
       </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3516,6 +4661,7 @@
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3540,6 +4686,7 @@
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3566,11 +4713,6 @@
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true; Partially achieved when all of the PA statements are true; Not achieved when at least one NA statement is true, or when neither set is fully met.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>[D1.a.NA.1] Your incident response plan is not documented.
 [D1.a.NA.2] Your incident response plan does not include your organisations identified essential function(s).
@@ -3587,21 +4729,55 @@
 [D1.a.A.4] Your incident response plan is communicated and understood by the business areas involved with the operation of your essential function(s).</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-PA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-PA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Partially achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#D97706
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3630,11 +4806,6 @@
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>[D1.b.NA.1] Inadequate arrangements have been made to make the right resources available to implement your response plan.
 [D1.b.NA.2] Your response team members are not equipped to make good response decisions and put them into effect.
@@ -3647,17 +4818,43 @@
 [D1.b.A.6] Arrangements exist to augment your organisation's incident response capabilities with external support if necessary (e.g. specialist cyber incident responders).</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3686,11 +4883,6 @@
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>[D1.c.NA.1] Exercises test only a discrete part of the process (e.g. that backups are working), but do not consider all areas.
 [D1.c.NA.2] Incident response exercises are not routinely carried out or are carried out in an ad-hoc way.
@@ -3702,16 +4894,40 @@
 [D1.c.A.4] Exercises test all parts of your response cycle relating to your essential function(s) (e.g. restoration of normal function(s) levels).</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3738,6 +4954,7 @@
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3764,11 +4981,6 @@
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>[D2.a.NA.1] You are not usually able to resolve incidents to a root cause or identify the contributing factors within a broader systems context.
 [D2.a.NA.2] You do not have a formal process for investigating causes.
@@ -3780,16 +4992,40 @@
 [D2.a.A.4] Your analysis considers what could have happened under plausible, alternative circumstances (e.g. ‘what if' / 'if only' scenarios).</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
@@ -3818,11 +5054,6 @@
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>CAF rule for this contributing outcome: Achieved when all of the A statements are true, otherwise Not achieved. This outcome has no Partially achieved level.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>[D2.b.NA.1] Following incidents, lessons learned are not captured or are limited in scope.
 [D2.b.NA.2] Improvements arising from lessons learned following an incident are not implemented or not given sufficient organisational priority.
@@ -3837,19 +5068,49 @@
 [D2.b.A.7] Your organisation learns from reported incidents in your sector and the wider national infrastructure.</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>TF-NA
+TF-NA
+TF-NA
+TF-NA
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A
+TF-A</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>TF-NA
-TF-NA
-TF-NA
-TF-NA
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A
-TF-A</t>
+          <t>Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Not achieved: at least one of the following statements is true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true
+Achieved: all the following statements are true</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>#DC2626
+#DC2626
+#DC2626
+#DC2626
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A
+#16A34A</t>
         </is>
       </c>
     </row>
